--- a/DLR.xlsx
+++ b/DLR.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -28,6 +28,12 @@
     <font>
       <name val="Aptos Narrow"/>
       <color rgb="000563C1"/>
+      <sz val="12"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="FF0563C1"/>
       <sz val="12"/>
       <u val="single"/>
     </font>
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,136 +472,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AD3"/>
+  <dimension ref="A2:AD3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="2">
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Q120</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Q220</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Q320</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Q420</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Q121</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Q221</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Q321</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Q421</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Q122</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Q222</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Q322</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Q422</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Q123</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Q223</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Q323</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Q423</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Q124</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Q224</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Q324</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Q424</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>Q125</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>Q225</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>Q325</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>Q425</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>Q126</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>Q226</t>
         </is>

--- a/DLR.xlsx
+++ b/DLR.xlsx
@@ -472,146 +472,457 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AD3"/>
+  <dimension ref="A1:CN3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
+    <row r="1"/>
     <row r="2">
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Q304</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Q404</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Q105</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Q205</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Q305</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Q405</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Q106</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Q206</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Q306</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Q406</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Q107</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Q207</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Q307</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Q407</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Q108</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Q208</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Q308</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Q408</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Q109</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Q209</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Q309</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Q409</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Q110</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Q210</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Q310</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Q410</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Q111</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Q211</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Q311</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Q411</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Q112</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Q212</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Q312</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Q412</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Q113</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Q213</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Q313</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>Q413</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Q114</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Q214</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Q314</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>Q414</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Q115</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>Q215</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Q315</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>Q415</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Q116</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Q216</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Q316</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>Q416</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>Q117</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>Q217</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>Q317</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>Q417</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>Q118</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>Q218</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Q318</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Q418</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>Q119</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>Q219</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>Q319</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>Q419</t>
+        </is>
+      </c>
+      <c r="BM2" s="2" t="inlineStr">
         <is>
           <t>Q120</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="BN2" s="2" t="inlineStr">
         <is>
           <t>Q220</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="BO2" s="2" t="inlineStr">
         <is>
           <t>Q320</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="BP2" s="2" t="inlineStr">
         <is>
           <t>Q420</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="BQ2" s="2" t="inlineStr">
         <is>
           <t>Q121</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="BR2" s="2" t="inlineStr">
         <is>
           <t>Q221</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="BS2" s="2" t="inlineStr">
         <is>
           <t>Q321</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="BT2" s="2" t="inlineStr">
         <is>
           <t>Q421</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="BU2" s="2" t="inlineStr">
         <is>
           <t>Q122</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="BV2" s="2" t="inlineStr">
         <is>
           <t>Q222</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="BW2" s="2" t="inlineStr">
         <is>
           <t>Q322</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="BX2" s="2" t="inlineStr">
         <is>
           <t>Q422</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="BY2" s="2" t="inlineStr">
         <is>
           <t>Q123</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="BZ2" s="2" t="inlineStr">
         <is>
           <t>Q223</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="CA2" s="2" t="inlineStr">
         <is>
           <t>Q323</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="CB2" s="2" t="inlineStr">
         <is>
           <t>Q423</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="CC2" s="2" t="inlineStr">
         <is>
           <t>Q124</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="CD2" s="2" t="inlineStr">
         <is>
           <t>Q224</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="CE2" s="2" t="inlineStr">
         <is>
           <t>Q324</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="CF2" s="2" t="inlineStr">
         <is>
           <t>Q424</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="CG2" s="2" t="inlineStr">
         <is>
           <t>Q125</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="CH2" s="2" t="inlineStr">
         <is>
           <t>Q225</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="CI2" s="2" t="inlineStr">
         <is>
           <t>Q325</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="CJ2" s="2" t="inlineStr">
         <is>
           <t>Q425</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="CK2" s="2" t="inlineStr">
         <is>
           <t>Q126</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="CL2" s="2" t="inlineStr">
         <is>
           <t>Q226</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>Q326</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>Q426</t>
         </is>
@@ -626,32 +937,32 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BM2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BN2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BP2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BQ2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BR2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BS2" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT2" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BU2" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BV2" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BW2" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BX2" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BY2" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BZ2" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CA2" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CB2" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CC2" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CD2" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CE2" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CF2" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CG2" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CH2" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI2" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CJ2" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CK2" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CL2" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DLR.xlsx
+++ b/DLR.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -34,6 +34,13 @@
     <font>
       <name val="Aptos Narrow"/>
       <color rgb="FF0563C1"/>
+      <sz val="12"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <i val="1"/>
+      <color rgb="FF7030A0"/>
       <sz val="12"/>
       <u val="single"/>
     </font>
@@ -58,10 +65,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -472,317 +480,316 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN3"/>
+  <dimension ref="A2:CN3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Q304</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Q404</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Q105</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Q205</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Q305</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Q405</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Q106</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Q206</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Q306</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Q406</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Q107</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Q207</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Q307</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Q407</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Q108</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Q208</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Q308</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Q408</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Q109</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Q209</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>Q309</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>Q409</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>Q110</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>Q210</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>Q310</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>Q410</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>Q111</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>Q211</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>Q311</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>Q411</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>Q112</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AH2" s="2" t="inlineStr">
         <is>
           <t>Q212</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>Q312</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>Q412</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AK2" s="2" t="inlineStr">
         <is>
           <t>Q113</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>Q213</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>Q313</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>Q413</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>Q114</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>Q214</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>Q314</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
         <is>
           <t>Q414</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>Q115</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AT2" s="2" t="inlineStr">
         <is>
           <t>Q215</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>Q315</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AV2" s="2" t="inlineStr">
         <is>
           <t>Q415</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AW2" s="2" t="inlineStr">
         <is>
           <t>Q116</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX2" s="2" t="inlineStr">
         <is>
           <t>Q216</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY2" s="2" t="inlineStr">
         <is>
           <t>Q316</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ2" s="2" t="inlineStr">
         <is>
           <t>Q416</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BA2" s="2" t="inlineStr">
         <is>
           <t>Q117</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BB2" s="2" t="inlineStr">
         <is>
           <t>Q217</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BC2" s="2" t="inlineStr">
         <is>
           <t>Q317</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BD2" s="2" t="inlineStr">
         <is>
           <t>Q417</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BE2" s="2" t="inlineStr">
         <is>
           <t>Q118</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BF2" s="2" t="inlineStr">
         <is>
           <t>Q218</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BG2" s="2" t="inlineStr">
         <is>
           <t>Q318</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BH2" s="2" t="inlineStr">
         <is>
           <t>Q418</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BI2" s="2" t="inlineStr">
         <is>
           <t>Q119</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BJ2" s="2" t="inlineStr">
         <is>
           <t>Q219</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BK2" s="2" t="inlineStr">
         <is>
           <t>Q319</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BL2" s="2" t="inlineStr">
         <is>
           <t>Q419</t>
         </is>
@@ -937,32 +944,94 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BM2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BN2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BP2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BQ2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BR2" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BS2" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT2" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BU2" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BV2" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BW2" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BX2" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BY2" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BZ2" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CA2" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CB2" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CC2" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CD2" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CE2" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CF2" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CG2" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CH2" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI2" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CJ2" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CK2" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CL2" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC2" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD2" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF2" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG2" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH2" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI2" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AJ2" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AK2" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL2" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AM2" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AN2" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO2" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AP2" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AQ2" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AR2" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AS2" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AT2" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU2" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV2" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AW2" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AX2" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY2" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA2" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB2" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BC2" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD2" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE2" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF2" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BG2" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BH2" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BI2" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BJ2" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BK2" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BL2" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BM2" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BN2" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO2" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BP2" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BQ2" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BR2" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BS2" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT2" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BU2" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BV2" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BW2" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BX2" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BY2" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BZ2" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CA2" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CB2" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CC2" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CD2" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CE2" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CF2" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CG2" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CH2" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI2" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CJ2" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CK2" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CL2" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DLR.xlsx
+++ b/DLR.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -44,6 +44,12 @@
       <sz val="12"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="FF595959"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -65,11 +71,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -144,6 +151,54 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>90</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>90</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -480,9 +535,451 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:CN3"/>
+  <dimension ref="A1:CN3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
+    <row r="1">
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AA1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AB1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AC1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AD1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AE1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AF1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AG1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AH1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AI1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AJ1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AK1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AL1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AM1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AN1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AO1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AP1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AQ1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AR1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AS1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AT1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AU1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AV1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AW1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AX1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AY1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AZ1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BA1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BB1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BC1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BD1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BE1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BF1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BG1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BH1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BI1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BJ1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BK1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BL1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BM1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BN1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BO1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BP1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BQ1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BR1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BS1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BT1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BU1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BV1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BW1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BX1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BY1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BZ1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CA1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CB1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="CC1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CD1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CE1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CF1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="CG1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CH1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CI1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CJ1" s="4" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="CK1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CL1" s="4" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -944,95 +1441,184 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC2" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD2" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF2" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG2" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH2" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI2" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AJ2" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AK2" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL2" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AM2" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AN2" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO2" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AP2" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AQ2" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AR2" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AS2" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AT2" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU2" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV2" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AW2" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AX2" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY2" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA2" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB2" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BC2" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD2" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE2" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF2" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BG2" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BH2" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BI2" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BJ2" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BK2" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BL2" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BM2" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BN2" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO2" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BP2" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BQ2" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BR2" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BS2" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT2" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BU2" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BV2" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BW2" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BX2" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BY2" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BZ2" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CA2" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CB2" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CC2" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CD2" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CE2" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CF2" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CG2" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CH2" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI2" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CJ2" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CK2" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CL2" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G1" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H1" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I1" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K1" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L1" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P1" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q1" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R1" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S1" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T1" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U1" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V1" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W1" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X1" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y1" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z1" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA1" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB1" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC1" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD1" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE1" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF1" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG1" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH1" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI1" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AJ1" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AK1" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL1" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AM1" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AN1" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO1" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AP1" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AQ1" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AR1" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AS1" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AT1" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU1" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV1" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AW1" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AX1" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY1" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ1" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA1" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB1" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BC1" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD1" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE1" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF1" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BG1" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BH1" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BI1" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BJ1" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BK1" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BL1" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BM1" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BN1" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO1" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BP1" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BQ1" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BR1" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BS1" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT1" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BU1" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BV1" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BW1" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BX1" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BY1" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BZ1" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CA1" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CB1" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CC1" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CD1" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CE1" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CF1" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CG1" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CH1" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI1" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CJ1" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CK1" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CL1" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC2" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD2" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF2" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG2" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH2" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI2" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AJ2" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AK2" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL2" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AM2" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AN2" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO2" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AP2" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AQ2" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AR2" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AS2" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AT2" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU2" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV2" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AW2" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AX2" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY2" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA2" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB2" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BC2" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD2" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE2" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF2" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BG2" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BH2" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BI2" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BJ2" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BK2" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BL2" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BM2" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BN2" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO2" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BP2" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BQ2" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BR2" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BS2" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT2" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BU2" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BV2" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BW2" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BX2" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BY2" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BZ2" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CA2" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CB2" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CC2" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CD2" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CE2" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CF2" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CG2" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CH2" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI2" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CJ2" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CK2" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CL2" r:id="rId176"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId177"/>
 </worksheet>
 </file>